--- a/CHECK LIST SS.HH DE LA CORPORACION (Respuestas).xlsx
+++ b/CHECK LIST SS.HH DE LA CORPORACION (Respuestas).xlsx
@@ -822,6 +822,7 @@
     <col width="15.38" customWidth="1" style="64" min="13" max="22"/>
     <col width="12" customWidth="1" style="64" min="19" max="19"/>
     <col width="12" customWidth="1" style="64" min="20" max="20"/>
+    <col width="16" customWidth="1" style="64" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="64">
@@ -925,7 +926,11 @@
           <t>PRIORIDAD</t>
         </is>
       </c>
-      <c r="U1" s="7" t="n"/>
+      <c r="U1" s="69" t="inlineStr">
+        <is>
+          <t>FECHA ATENCION</t>
+        </is>
+      </c>
       <c r="V1" s="7" t="n"/>
     </row>
     <row r="2" ht="22.5" customHeight="1" s="64">
